--- a/daily_matches/job_matches_2026-09-09.xlsx
+++ b/daily_matches/job_matches_2026-09-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apptium Technologies</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, BigQuery, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Terraform, Kafka, Hadoop, NoSQL, Tableau, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd14e10f528b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbe5469b433e310</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI</t>
+          <t>LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d19e49393e61c3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Senior Cybersecurity Engineer I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=516c0cec840edf60</t>
+          <t>https://www.indeed.com/viewjob?jk=0da6ff0729dbc15e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.4</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI</t>
+          <t>RAG, S3, Glue, Athena, Git, PySpark, Kafka, Hadoop, Quicksight, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=014c5701f0f8c8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=39ca6ce91460b142</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Dir Data Warehouse Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.4</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI</t>
+          <t>Gemini, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcb99e6f3d7d62f</t>
+          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8113d275f4e8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=aac4b33e635a5e80</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>22.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0037a04643c403d</t>
+          <t>https://www.indeed.com/viewjob?jk=80e719ce5a357916</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Mistral, Prompt Engineering, Cortex, TensorFlow, PyTorch</t>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f254bc9e9edf4fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=644cb53cf368cd5e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>KINECTIVE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Mistral, Prompt Engineering, Cortex, TensorFlow, PyTorch</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6caa87d7af8f56</t>
+          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer — AI Platform Engineering</t>
+          <t>Software Development Intern</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Athena, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11261eef85e22149</t>
+          <t>https://www.indeed.com/viewjob?jk=f0b7932e2f1a789a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Gen AI Engineer</t>
+          <t>AI Engineer, Innovation &amp; AI (contract)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Interaslabs</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Stoughton, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering, Docker</t>
+          <t>AI Engineer, Generative AI, LangChain, Copilot, CI/CD, Git, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2353909d571ba54</t>
+          <t>https://www.indeed.com/viewjob?jk=f28f1c59ab76f307</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
+          <t>AI Engineer, Data Science Team- Boise, ID</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, S3, Glue, Athena, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87f3f2554ec8def</t>
+          <t>https://www.indeed.com/viewjob?jk=133a163060754829</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rackspace Technology</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Data Lake, Docker, Kubernetes, CI/CD, NoSQL</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44020682d86faf54</t>
+          <t>https://www.indeed.com/viewjob?jk=b6aa2dd2deec446d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer II – Generative AI &amp; LLM Platforms</t>
+          <t>Scientific Software Engineer | Kumar Lab</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, PyTorch, S3, Kubernetes, CI/CD, Git</t>
+          <t>RAG, Copilot, PyTorch, Kubernetes, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51506997cf019eed</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c9b0d32a9f517c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Architect Engineer - ELR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EarnIn</t>
+          <t>Avalara</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LLaMA, Copilot, Pinecone, Prompt Engineering, PyTorch, MLflow, Docker, Git</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659de9b3e649bc7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d53c99029aaeed43</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Senior Software Engineer - APIs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Unacast</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, Python</t>
+          <t>Generative AI, RAG, Data Lake, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bbe88bca6b12e7</t>
+          <t>https://www.indeed.com/viewjob?jk=3e291e8d8f892017</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Business Intelligence Developer I - Power BI (CEMI)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Weill Cornell Medicine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, Python</t>
+          <t>Generative AI, RAG, Redshift, Dataflow, Redshift, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00e4985a172439e4</t>
+          <t>https://www.indeed.com/viewjob?jk=68dfbfe981d822d4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior AI/ML Engineer - Validation &amp; Evaluation</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Katalyst Data Management</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5ab3490cf1d4af</t>
+          <t>https://www.indeed.com/viewjob?jk=426a9e1622fd3bd1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Remote)</t>
+          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Yoodli AI Roleplays</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Akron, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, Kinesis, CI/CD, Terraform, Git, Redshift, Python, SQL</t>
+          <t>RAG, Kubernetes, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3cc1b67d583e3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer- Backend (Roleplays)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Western Camps, Inc.</t>
+          <t>Yoodli AI Roleplays</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
+          <t>Generative AI, Kubernetes, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f95780f32f3fa1c</t>
+          <t>https://www.indeed.com/viewjob?jk=368eca5e5b0d8403</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Speech &amp; LLM Training Data</t>
+          <t>Senior AI Behavioral Scientist &amp; Product Analyst (10522)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Extreme Networks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Hugging Face, PyTorch, S3, Glue, MLflow, Docker, Git, Databricks, PySpark</t>
+          <t>AI Engineer, RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807824f66dc0a84a</t>
+          <t>https://www.indeed.com/viewjob?jk=c36c24af0849b81f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NLP AI Engineer</t>
+          <t>AI &amp; Analytics Implementation Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, PyTorch, Docker, Kubernetes, Python, R</t>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da38be37ad0995c</t>
+          <t>https://www.indeed.com/viewjob?jk=9400bda7e66e72ae</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Conversational AI Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AURA TECHNOLOGIES LLC.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Kubernetes, CI/CD, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9f0ebe32bfd9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d135756d51de1f77</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Domain Consultant 2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d46de95576211b34</t>
+          <t>https://www.indeed.com/viewjob?jk=76bf702cd7c9d64e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Chicago)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Copilot, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0690835de0e1aab</t>
+          <t>https://www.indeed.com/viewjob?jk=f077a441b93563b3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Dallas)</t>
+          <t>Senior Research Software Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chapel Hill, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa37629ae83aa444</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff03616a3dbef4e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Experienced AI Engineer - Generative AI/Machine Learning</t>
+          <t>Senior Software Engineer, Core Infrastructure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RLI</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Peoria, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fecd4bc6ea547b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8b5421aefdd38e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>AI Researcher</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>Data Scientist, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf21b46341bfdf2</t>
+          <t>https://www.indeed.com/viewjob?jk=55dd7abbea55abb8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Senior Software Engineering Architect — Investment Technologies</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Terraform, Snowflake, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5427c3decfca9bb</t>
+          <t>https://www.indeed.com/viewjob?jk=5f64103e46352281</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, Copilot, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc32b768ab683d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=095c32e83e37f1b7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Analyst, Clinical Operations</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Snowflake, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8307d2d60f9fabd5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d481832123b10a1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Intern (AI)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>iCatalyst</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dcdca24f24f570c</t>
+          <t>https://www.indeed.com/viewjob?jk=4e381d6b74394f9c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Camunda Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,917 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c957d439dd62b1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27be9e40a62f0614</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4976c9d6fddbb4ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Sr Software Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Michaels</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Jenkins, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8a78e43645a938</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Data Engineering Intern - AI &amp; Analytics (January - August 2027)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16c8d1de2eff4f7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Sr. Quality Assurance Analyst</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Broadcast Music</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d059a9776583fb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Software engineer, connectors &amp; MCP</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Writer</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e676a2241a47f790</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Software engineer, connectors &amp; MCP</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Writer</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67d529fb27aef4f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Software engineer, connectors &amp; MCP</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Writer</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=589e973f4149bda5</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Gallup</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9514aafacda170</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior Platform DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Technosoft Engineering, INC</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e238b69e3583240</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Senior Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Reserv</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b393b7062df51c5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Current PhD, AI Engineering Internship Program - Summer 2027</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, PyTorch, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cecf89aa74add10</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Current Master's, AI Engineering Internship Program - Summer 2027</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, PyTorch, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=090d35a483acfe11</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Generative AI, CI/CD, Databricks, PySpark, Tableau, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2851eefe207f3714</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Ingram Content Group</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>La Vergne, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f18d280c2406bef</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Data Scientist Senior Associate — Business Observability &amp; AI Platform</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, AKS, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd293c80da3b13a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Data Science Intern</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e560eb63c5bd470c</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Data Science Intern</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97c1bb3e6842a2b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Founding Product Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Veedma</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, AKS, Git, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69c96e4949016f22</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Resident Solution Architect (RSA)</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Databricks, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6994995b30cde1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Resident Solution Architect (Databricks)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Databricks, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2098cfbc186ec6d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>LTM Limited</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a76db7baaf915fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Resident Solution Architect (RSA)</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Databricks, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff59b562289e9873</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Resident Solution Architect (Databricks)</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Databricks, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e41fc772140be3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Dover, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, OpenCV, YOLO, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a01e9f4dc7c725</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Quantitative Analyst Intern</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Talos Global</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, BigQuery, Python, SQL, R, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d5d2b7f11ee324aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bddc1653f7eeea8a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-09.xlsx
+++ b/daily_matches/job_matches_2026-09-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Terraform, Kafka, Hadoop, NoSQL, Tableau, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, Data Lake, Dataflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bbe5469b433e310</t>
+          <t>https://www.indeed.com/viewjob?jk=b64978da5029f9c3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes, Jenkins, Terraform, Git</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, Data Lake, Dataflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
+          <t>https://www.indeed.com/viewjob?jk=daaa8d1691a560b0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Engineer I</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da6ff0729dbc15e</t>
+          <t>https://www.indeed.com/viewjob?jk=8abf54fe3b7ea01b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Git, PySpark, Kafka, Hadoop, Quicksight, Python</t>
+          <t>RAG, Copilot, Prompt Engineering, Glue, Data Lake, Docker, CI/CD, Git, Databricks, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ca6ce91460b142</t>
+          <t>https://www.indeed.com/viewjob?jk=14c4f20a82a492aa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dir Data Warehouse Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gemini, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift, Python</t>
+          <t>Kinesis, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, Polars, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
+          <t>https://www.indeed.com/viewjob?jk=8571eee74fa37144</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>Kinesis, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, Polars, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac4b33e635a5e80</t>
+          <t>https://www.indeed.com/viewjob?jk=5306f5b43c1fe61a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>Kinesis, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, Polars, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e719ce5a357916</t>
+          <t>https://www.indeed.com/viewjob?jk=6250b6d758b24165</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644cb53cf368cd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb6a851d163dda0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Network Engineer</t>
+          <t>Data Engineer - xLT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KINECTIVE</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Synapse, Data Lake, Dataflow, Git, Snowflake, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
+          <t>https://www.indeed.com/viewjob?jk=24527e4fd5602bee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Development Intern</t>
+          <t>Java AWS Backend Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0b7932e2f1a789a</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdfad2616ee54a9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer, Innovation &amp; AI (contract)</t>
+          <t>Java AWS Backend Developer (Dallas, TX)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, Copilot, CI/CD, Git, MongoDB, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28f1c59ab76f307</t>
+          <t>https://www.indeed.com/viewjob?jk=335ed21784f1defe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Science Team- Boise, ID</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>LLR Partners</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+          <t>AI Engineer, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=133a163060754829</t>
+          <t>https://www.indeed.com/viewjob?jk=eeff0e9a44ea1590</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Data Engineer, Growth</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Superhuman</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Kafka, SQL, R</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6aa2dd2deec446d</t>
+          <t>https://www.indeed.com/viewjob?jk=db35ae430267ee9d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer | Kumar Lab</t>
+          <t>Java AWS Backend Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, PyTorch, Kubernetes, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c9b0d32a9f517c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9bea0e142bf653</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Architect Engineer - ELR</t>
+          <t>Java AWS Backend Developer (Dallas, TX)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d53c99029aaeed43</t>
+          <t>https://www.indeed.com/viewjob?jk=57d584755e421437</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - APIs</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unacast</t>
+          <t>ImmunityBio</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e291e8d8f892017</t>
+          <t>https://www.indeed.com/viewjob?jk=45332980cb789d6b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer I - Power BI (CEMI)</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Weill Cornell Medicine</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Redshift, Dataflow, Redshift, Power BI, Python, SQL, R, Optimization</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68dfbfe981d822d4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8e2b60f9187848</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer - Validation &amp; Evaluation</t>
+          <t>Software Engineer III - IBM i (AS/400) Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426a9e1622fd3bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=16bd55c95eee8fe8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
+          <t>Actuarial Data Scientist-Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yoodli AI Roleplays</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
+          <t>https://www.indeed.com/viewjob?jk=46126d6f4852b55b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Backend (Roleplays)</t>
+          <t>Sr Data Scientist (remote)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yoodli AI Roleplays</t>
+          <t>US Foods</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, Kubernetes, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, Data Lake, CI/CD, Git, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368eca5e5b0d8403</t>
+          <t>https://www.indeed.com/viewjob?jk=08cd93427986947c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Behavioral Scientist &amp; Product Analyst (10522)</t>
+          <t>Core Java &amp; UI Developer Expert (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Extreme Networks</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala, A/B Testing</t>
+          <t>RAG, S3, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c36c24af0849b81f</t>
+          <t>https://www.indeed.com/viewjob?jk=c619aca7e5e021af</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI &amp; Analytics Implementation Specialist</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Wondr Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9400bda7e66e72ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ad29ceca49210f1b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Marketing Engineer, AI Visibility</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AURA TECHNOLOGIES LLC.</t>
+          <t>Tallwave</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
+          <t>RAG, Gemini, CI/CD, Git, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d135756d51de1f77</t>
+          <t>https://www.indeed.com/viewjob?jk=f391179f166f30cc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Domain Consultant 2</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bf702cd7c9d64e</t>
+          <t>https://www.indeed.com/viewjob?jk=2602c0fe6a2e7651</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer - Application Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, S3, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f077a441b93563b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ce39479fe79521</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Research Software Developer</t>
+          <t>Sr Software Engineer in Test</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>University of North Carolina at Chapel Hill</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chapel Hill, NC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff03616a3dbef4e</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd1580c3be9bf70</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Core Infrastructure</t>
+          <t>2027 Quantitative Analytics Program – Applied Computational Intelligence (ACI Masters) – Early Careers</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8b5421aefdd38e</t>
+          <t>https://www.indeed.com/viewjob?jk=d8209a997f5a2012</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Researcher</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,192 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55dd7abbea55abb8</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Software Engineering Architect — Investment Technologies</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>RGA</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Terraform, Snowflake, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f64103e46352281</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Gallagher</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Rolling Meadows, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Copilot, CI/CD, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=095c32e83e37f1b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst, Clinical Operations</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Snowflake, Tableau, Power BI, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d481832123b10a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Technical Intern (AI)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>iCatalyst</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e381d6b74394f9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Camunda Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Fidelity TalentSource</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Westlake, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bddc1653f7eeea8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5af0994d70a5d18e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-09.xlsx
+++ b/daily_matches/job_matches_2026-09-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Senior Software Engineer – Cloud Data Solutions</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Coral Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, Data Lake, Dataflow, CI/CD, Terraform</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kubernetes, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,112 +496,112 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b64978da5029f9c3</t>
+          <t>https://www.indeed.com/viewjob?jk=4c874c000ec76150</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, Data Lake, Dataflow, CI/CD, Terraform</t>
+          <t>Data Scientist, Generative AI, Prompt Engineering, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaa8d1691a560b0</t>
+          <t>https://www.indeed.com/viewjob?jk=76c1021a7b6a47a3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, Generative AI, Prompt Engineering, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abf54fe3b7ea01b</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb7f514c771de53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Glue, Data Lake, Docker, CI/CD, Git, Databricks, MongoDB</t>
+          <t>Data Scientist, Generative AI, Prompt Engineering, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c4f20a82a492aa</t>
+          <t>https://www.indeed.com/viewjob?jk=5d6c2efe2d967ca1</t>
         </is>
       </c>
     </row>
@@ -613,30 +613,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kinesis, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, Polars, Python, SQL</t>
+          <t>Data Scientist, Generative AI, Prompt Engineering, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8571eee74fa37144</t>
+          <t>https://www.indeed.com/viewjob?jk=d94535e52011728f</t>
         </is>
       </c>
     </row>
@@ -648,152 +648,152 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kinesis, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, Polars, Python, SQL</t>
+          <t>Data Scientist, Generative AI, Prompt Engineering, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5306f5b43c1fe61a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bc8d7737feba10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>OSS Engineer (US - Remote)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Axon Networks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kinesis, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, Polars, Python, SQL</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6250b6d758b24165</t>
+          <t>https://www.indeed.com/viewjob?jk=110b991660ad2978</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Software Development Engineer III, Advertising Technology</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb6a851d163dda0</t>
+          <t>https://www.indeed.com/viewjob?jk=e50438ce8a20e87b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - xLT</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CampusWorks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Dataflow, Git, Snowflake, PySpark, Power BI, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, MLflow, FastAPI, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24527e4fd5602bee</t>
+          <t>https://www.indeed.com/viewjob?jk=bdbbfac9ef317da1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java AWS Backend Developer</t>
+          <t>Research Engineer, Institute for Software Integrated Systems</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, R</t>
+          <t>FastAPI, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Julia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdfad2616ee54a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cae2006dbac4b5b2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java AWS Backend Developer (Dallas, TX)</t>
+          <t>Senior Data Scientist - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, R</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=335ed21784f1defe</t>
+          <t>https://www.indeed.com/viewjob?jk=c997c217f22c6f3e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Architecture Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LLR Partners</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeff0e9a44ea1590</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2a31af441ea2a8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer, Growth</t>
+          <t>Security Specialist, Vulnerability Management (US - Remote)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Superhuman</t>
+          <t>Axon Networks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db35ae430267ee9d</t>
+          <t>https://www.indeed.com/viewjob?jk=b8811f97085790bb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java AWS Backend Developer</t>
+          <t>Senior AI Infrastructure Engineer, Kubernetes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Firmus Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, R</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9bea0e142bf653</t>
+          <t>https://www.indeed.com/viewjob?jk=0e2abb8723e3b204</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java AWS Backend Developer (Dallas, TX)</t>
+          <t>Senior DevSecOps &amp; Network Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KWI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, R</t>
+          <t>Copilot, Docker, CI/CD, Terraform, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,462 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d584755e421437</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ImmunityBio</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>El Segundo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45332980cb789d6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Integration Platform Developer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8e2b60f9187848</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer III - IBM i (AS/400) Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16bd55c95eee8fe8</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Actuarial Data Scientist-Remote</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Mutual of Omaha</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46126d6f4852b55b</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sr Data Scientist (remote)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>US Foods</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Rosemont, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, Data Lake, CI/CD, Git, Python, SQL, R, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08cd93427986947c</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Core Java &amp; UI Developer Expert (Onsite Hybrid)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c619aca7e5e021af</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Wondr Health</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29ceca49210f1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Marketing Engineer, AI Visibility</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Tallwave</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, CI/CD, Git, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f391179f166f30cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Mule ESB Developer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2602c0fe6a2e7651</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Application Architect</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Hopkins, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, S3, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ce39479fe79521</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Roche</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd1580c3be9bf70</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2027 Quantitative Analytics Program – Applied Computational Intelligence (ACI Masters) – Early Careers</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8209a997f5a2012</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Lehi, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5af0994d70a5d18e</t>
+          <t>https://www.indeed.com/viewjob?jk=db7570104180c320</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-09.xlsx
+++ b/daily_matches/job_matches_2026-09-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Data Solutions</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Coral Springs, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kubernetes, Git, Snowflake, Redshift</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c874c000ec76150</t>
+          <t>https://www.indeed.com/viewjob?jk=10a3b9d686f61d33</t>
         </is>
       </c>
     </row>
@@ -508,195 +508,195 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Prompt Engineering, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka</t>
+          <t>RAG, S3, Glue, Redshift, Synapse, Docker, Kubernetes, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c1021a7b6a47a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6bedb030ec88c051</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI intern</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Graco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>French Lake, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Prompt Engineering, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, EC2, Glue, MLflow, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb7f514c771de53</t>
+          <t>https://www.indeed.com/viewjob?jk=22a78208d6b133be</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Graco</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>French Lake, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Prompt Engineering, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, EC2, Glue, MLflow, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d6c2efe2d967ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed23c206ff17c0b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Prompt Engineering, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka</t>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94535e52011728f</t>
+          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Automation QE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Prompt Engineering, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bc8d7737feba10</t>
+          <t>https://www.indeed.com/viewjob?jk=76d03aaffe8965fd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OSS Engineer (US - Remote)</t>
+          <t>Cloud Back End Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110b991660ad2978</t>
+          <t>https://www.indeed.com/viewjob?jk=979c2d51bf327a22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development Engineer III, Advertising Technology</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, PyTorch, Keras, CI/CD, Terraform, Git, Snowflake, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e50438ce8a20e87b</t>
+          <t>https://www.indeed.com/viewjob?jk=04e6bb06610c32bf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Mid/Senior-level GoLang Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CampusWorks</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, MLflow, FastAPI, Databricks, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbbfac9ef317da1</t>
+          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Research Engineer, Institute for Software Integrated Systems</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>OLYMPIA PHARMACEUTICALS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Julia</t>
+          <t>S3, EC2, FastAPI, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae2006dbac4b5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=cb3047b837f1fedf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Remote</t>
+          <t>AI Engineer, Enterprise AI Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Camping World</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Hypothesis Testing</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, MLflow, Docker, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c997c217f22c6f3e</t>
+          <t>https://www.indeed.com/viewjob?jk=d593ed18a7eaef04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Architecture Engineer</t>
+          <t>AI Engineer, Enterprise AI Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>Camping World</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, MLflow, Docker, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2a31af441ea2a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee18a654788e5998</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Security Specialist, Vulnerability Management (US - Remote)</t>
+          <t>Sr. Applied AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Docker, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8811f97085790bb</t>
+          <t>https://www.indeed.com/viewjob?jk=378629ea0316dd46</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Infrastructure Engineer, Kubernetes</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Firmus Technologies</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, AWS SageMaker, CI/CD, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,1617 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2abb8723e3b204</t>
+          <t>https://www.indeed.com/viewjob?jk=e600949f95b627d9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevSecOps &amp; Network Infrastructure Engineer</t>
+          <t>Sr. Software Engineer, Growth</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KWI</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Docker, Kubernetes, BigQuery, PostgreSQL, MySQL, SQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f81b2fbe5ef9339</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Applied AI/ML Senior Associate</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, spaCy, MLflow, FastAPI, Apache Airflow, CI/CD, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8db018dc22b7af39</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LEADER BANK</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Arlington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d21460f2f100edf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Vector Bidding Science</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, BigQuery, Git, BigQuery, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d787a01b173ebb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Vector Bidding Science</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Olympia, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, BigQuery, Git, BigQuery, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=958a6b34872bba31</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr. AI DevOps Developer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sbt Global</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9647e6f98f029060</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Summer Associate Internship (Data Scientist)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Navy Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, AKS, Git, Databricks, PySpark, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7acb22fc1d33df6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Azure Architect - Managed Services</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Quisitive</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d9680f06d024613</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Terraform, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b78ae98ab2be932f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (Python, AI/ML, Generative AI)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Modus Create</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e16dd4599811f63</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Java Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce9c740d41490771</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Engineer III - Network Planning</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Verizon</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, BigQuery, BigQuery, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b77b41470f1ccaa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr. Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d653f84741fe779</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Summer Associate Internship (Business Intelligence Analyst)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Navy Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Copilot, Git, Databricks, PySpark, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4613876632d673e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Solution Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Experian</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=549bd67dfaf059ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Happen Bank</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2390c91100957431</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Happen Bank</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=410d6c6a010f035c</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MISO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa1b527dd1418591</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst III</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Amerant Bank</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Miramar, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcd8ca853221f130</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Healthfirst</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, EC2, Redshift, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efaa4f7628fd5494</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Science, AI and Business Analyst</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Coherent Corp.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, LLaMA, Gemini, Prompt Engineering, Tableau, Matplotlib, Python, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3990b0bade9560b</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Copilot, Docker, CI/CD, Terraform, Git, MySQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db7570104180c320</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Synapse, CI/CD, NoSQL, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f283cdf14c51be80</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Synapse, CI/CD, NoSQL, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f941f33cf05ed3e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Synapse, CI/CD, NoSQL, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c26de86ee4d0e9bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, AISWP (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51a479fa3c092ca4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Simulation platform)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6b5351219bf2547</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Application Developer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nyla Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f44d08286c58499</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Summer Associate Internship (Associate Data Engineer)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Navy Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa822ad66fbbecb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Summer Associate Internship (Fraud Data Governance)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Navy Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fa247b105a8195a</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LangChain, Copilot, FastAPI, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7428046fd4814575</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TECHNICAL ARCHITECT</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Coforge</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=451c85614970c518</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LTSS &amp; Dual Eligible Program Report Developer IV</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CareSource</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>CI/CD, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfded12dd2b38a6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Web Marketing Intern - Digital Experience Analytics</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=729f111f1f5c76c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AI Automation &amp; Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>National Reliance Group</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed94ddca3f458482</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Agentic Ontology Software Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AI Engineer, Docker, Kubernetes, CI/CD, Databricks, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a626a3cd118d52e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Agentic Ontology Software Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Docker, Kubernetes, CI/CD, Databricks, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b670276af9926c71</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Operations Research</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>United Airlines</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, AKS, Git, Python, R, Java, Julia, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87c621fc267b5484</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Summer Associate Internship (Data Scientist)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Navy Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Databricks, PySpark, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fc04cf7be8145d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Summer Associate Internship (Data Scientist)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Navy Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, AKS, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a3d8c9d84926055</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Summer Associate Intern (Data Scientist)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Navy Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Hadoop, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8866ba9d53533503</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Associate Data &amp; AI Analyst</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>L.E.K. Consulting</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=590e3db19d4894a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst- Banking</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>S3, Databricks, PySpark, Tableau, Power BI, Quicksight, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a5952e9be4a6a22</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst- Banking</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>S3, Databricks, PySpark, Tableau, Power BI, Quicksight, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c37dedc442852930</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Test Automation Engineer - Playwright</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5324d745cd541ec0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Developer - Information Technology</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>United Airlines</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df097d34a81a814f</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Perry Weather</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, CI/CD, Snowflake, Databricks, Kafka, SQL, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20aa9baf24b5cbe8</t>
         </is>
       </c>
     </row>
